--- a/output/Weekly_Schedule_Summary_normal.xlsx
+++ b/output/Weekly_Schedule_Summary_normal.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -597,16 +597,16 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="K3" t="n">
-        <v>77.51000000000001</v>
+        <v>43.13</v>
       </c>
       <c r="L3" t="n">
-        <v>84.53</v>
+        <v>49.72</v>
       </c>
       <c r="M3" t="n">
-        <v>117.51</v>
+        <v>139.13</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
